--- a/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:52</t>
+          <t>2026-08-28 06:58:58</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:53</t>
+          <t>2026-08-28 06:58:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:55</t>
+          <t>2026-08-28 06:59:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>-0.28%14300</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>14340</v>
+        <v>14300</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.43%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>-5.93%1110</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-5.93%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1180</v>
+        <v>1110</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5500</v>
+        <v>5490</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+2.49%2055</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2055</v>
+        <v>2260</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6915</v>
+        <v>7065</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2090</v>
+        <v>2125</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+9.62%1310</t>
+          <t>-3.44%1265</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+9.62%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.65%620</t>
+          <t>+10%682</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>620</v>
+        <v>682</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.37%179.5</t>
+          <t>-0.84%178</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>179.5</v>
+        <v>178</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.27%116.5</t>
+          <t>+7.73%125.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>+7.73%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>116.5</v>
+        <v>125.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.9%227.5</t>
+          <t>-3.08%220.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>227.5</v>
+        <v>220.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:58</t>
+          <t>2026-08-28 15:44:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.17%433</t>
+          <t>+0.23%434</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.96%422.5</t>
+          <t>+7.46%454</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+7.46%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>422.5</v>
+        <v>454</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1770</v>
+        <v>1830</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3865</v>
+        <v>3985</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+1.6%6015</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5920</v>
+        <v>6015</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.27%3870</t>
+          <t>+5.04%4065</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3870</v>
+        <v>4065</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+3.75%914</t>
+          <t>-1.64%899</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6815</v>
+        <v>7200</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+5.3%477</t>
+          <t>+0.73%480.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>477</v>
+        <v>480.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1295</v>
+        <v>1240</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+3.53%3370</t>
+          <t>-1.93%3305</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3370</v>
+        <v>3305</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.43%563</t>
+          <t>+3.37%582</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.43%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.95%301</t>
+          <t>+5.48%317.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>301</v>
+        <v>317.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2%784</t>
+          <t>-1.15%775</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2%</t>
+          <t>-1.15%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:59</t>
+          <t>2026-08-28 15:44:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+10%1430</t>
+          <t>-4.55%1365</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1430</v>
+        <v>1365</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.31%968</t>
+          <t>-0.31%965</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5645</v>
+        <v>5785</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.88%90.3</t>
+          <t>+0.22%90.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>90.3</v>
+        <v>90.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+9.93%675</t>
+          <t>+9.93%742</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>675</v>
+        <v>742</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.85%345</t>
+          <t>+1.16%349</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>15305</v>
+        <v>15630</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.46%1075</t>
+          <t>0%1075</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+3.11%1490</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.67%1490</t>
+          <t>-1.34%1470</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1490</v>
+        <v>1470</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:59:00</t>
+          <t>2026-08-28 15:44:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.66%151</t>
+          <t>+1.32%153</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">

--- a/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.52%260,000</t>
+          <t>8.42%260,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.52%</t>
+          <t>8.42%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.64%1,001,000</t>
+          <t>7.62%1,001,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.64%</t>
+          <t>7.62%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.20%1,306,000</t>
+          <t>7.16%1,306,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.20%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.70%2,482,000</t>
+          <t>6.24%2,482,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.70%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5490</v>
+        <v>2260</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.85%465,000</t>
+          <t>5.94%1,161,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5.94%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>465000</v>
+        <v>1161000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2260</v>
+        <v>5490</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.45%1,161,000</t>
+          <t>5.78%465,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.78%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1161000</v>
+        <v>465000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.42%343,000</t>
+          <t>5.49%343,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.13%1,074,000</t>
+          <t>5.17%1,074,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.17%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.88%1,630,000</t>
+          <t>4.67%1,630,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.67%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.16%2,231,000</t>
+          <t>3.45%2,231,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>1815富喬</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+7.73%125.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+7.73%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5030</v>
+        <v>125.5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.12%268,000</t>
+          <t>3.09%10,877,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>268000</v>
+        <v>10877000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.84%178</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>178</v>
+        <v>5030</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.97%7,245,000</t>
+          <t>3.05%268,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7245000</v>
+        <v>268000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1815富喬</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+7.73%125.5</t>
+          <t>-0.84%178</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+7.73%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>125.5</v>
+        <v>178</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.90%10,877,000</t>
+          <t>2.92%7,245,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>10877000</v>
+        <v>7245000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>8021尖點</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-3.08%220.5</t>
+          <t>+7.46%454</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>+7.46%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>220.5</v>
+        <v>454</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.83%5,445,000</t>
+          <t>2.76%2,682,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.76%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5445000</v>
+        <v>2682000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:15</t>
+          <t>2026-08-28 17:25:25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.23%434</t>
+          <t>-3.08%220.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>434</v>
+        <v>220.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.73%2,753,000</t>
+          <t>2.72%5,445,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.72%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2753000</v>
+        <v>5445000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8021尖點</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+7.46%454</t>
+          <t>+0.23%434</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+7.46%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.59%2,682,000</t>
+          <t>2.71%2,753,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2682000</v>
+        <v>2753000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1830</v>
+        <v>3985</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.56%632,000</t>
+          <t>2.40%266,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.56%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>632000</v>
+        <v>266000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>+1.6%6015</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3985</v>
+        <v>6015</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.35%266,000</t>
+          <t>2.23%164,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>266000</v>
+        <v>164000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.6%6015</t>
+          <t>+5.04%4065</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6015</v>
+        <v>4065</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.22%164,000</t>
+          <t>1.98%215,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>164000</v>
+        <v>215000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+5.04%4065</t>
+          <t>-1.64%899</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+5.04%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4065</v>
+        <v>899</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.90%215,000</t>
+          <t>1.72%844,013</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>215000</v>
+        <v>844013</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.64%899</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>899</v>
+        <v>1830</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.76%844,013</t>
+          <t>1.58%382,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>844013</v>
+        <v>382000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.20%77,000</t>
+          <t>1.26%77,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.99%716,000</t>
+          <t>1.01%716,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.89%300,000</t>
+          <t>0.84%300,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.93%3305</t>
+          <t>+3.37%582</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+3.37%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3305</v>
+        <v>582</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.49%63,000</t>
+          <t>0.49%373,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>63000</v>
+        <v>373000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,34 +2090,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.37%582</t>
+          <t>+5.48%317.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.37%</t>
+          <t>+5.48%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>582</v>
+        <v>317.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.48%373,000</t>
+          <t>0.47%659,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>373000</v>
+        <v>659000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+5.48%317.5</t>
+          <t>-1.93%3305</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+5.48%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>317.5</v>
+        <v>3305</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.45%659,000</t>
+          <t>0.47%63,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>659000</v>
+        <v>63000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.45%250,000</t>
+          <t>0.44%250,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:17</t>
+          <t>2026-08-28 17:25:26</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.55%1365</t>
+          <t>+9.93%742</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1365</v>
+        <v>742</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.44%134,000</t>
+          <t>0.44%261,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>134000</v>
+        <v>261000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.31%965</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>965</v>
+        <v>5785</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.43%196,000</t>
+          <t>0.43%33,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>196000</v>
+        <v>33000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>-0.31%965</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5785</v>
+        <v>965</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.43%33,000</t>
+          <t>0.43%196,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>33000</v>
+        <v>196000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.22%90.5</t>
+          <t>-4.55%1365</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>90.5</v>
+        <v>1365</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.40%1,957,000</t>
+          <t>0.41%134,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1957000</v>
+        <v>134000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+9.93%742</t>
+          <t>+1.16%349</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>742</v>
+        <v>349</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.40%261,000</t>
+          <t>0.40%508,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>261000</v>
+        <v>508000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.16%349</t>
+          <t>+0.22%90.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>349</v>
+        <v>90.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.40%508,000</t>
+          <t>0.40%1,957,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>508000</v>
+        <v>1957000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.38%11,000</t>
+          <t>0.39%11,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%1075</t>
+          <t>+3.11%1490</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1075</v>
+        <v>1490</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.38%155,000</t>
+          <t>0.38%113,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,11 +2727,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>155000</v>
+        <v>113000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+3.11%1490</t>
+          <t>0%1075</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1490</v>
+        <v>1075</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.37%113,000</t>
+          <t>0.38%155,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>113000</v>
+        <v>155000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.34%99,952</t>
+          <t>0.33%99,952</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:18</t>
+          <t>2026-08-28 17:25:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:25</t>
+          <t>2026-08-28 19:07:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:26</t>
+          <t>2026-08-28 19:07:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:27</t>
+          <t>2026-08-28 19:07:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:48</t>
+          <t>2026-08-28 20:38:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:49</t>
+          <t>2026-08-28 20:38:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 19:07:51</t>
+          <t>2026-08-28 20:38:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:40</t>
+          <t>2026-08-28 21:41:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:41</t>
+          <t>2026-08-28 21:41:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:43</t>
+          <t>2026-08-28 21:41:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:32</t>
+          <t>2026-08-28 21:46:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:33</t>
+          <t>2026-08-28 21:46:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:34</t>
+          <t>2026-08-28 21:46:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
